--- a/exemplos/output/payroll-02.xlsx
+++ b/exemplos/output/payroll-02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="98">
   <si>
     <t>Pág.</t>
   </si>
@@ -127,45 +127,33 @@
     <t>630,36</t>
   </si>
   <si>
-    <t>433,20</t>
-  </si>
-  <si>
-    <t>61,88</t>
-  </si>
-  <si>
-    <t>185,65</t>
+    <t>0,90</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>0,38</t>
   </si>
   <si>
     <t>621,03</t>
   </si>
   <si>
-    <t>473,44</t>
+    <t>3,26</t>
+  </si>
+  <si>
+    <t>12,89</t>
+  </si>
+  <si>
+    <t>67,72</t>
+  </si>
+  <si>
+    <t>0,54</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>0,90</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>0,38</t>
-  </si>
-  <si>
-    <t>3,26</t>
-  </si>
-  <si>
-    <t>12,89</t>
-  </si>
-  <si>
-    <t>67,72</t>
-  </si>
-  <si>
-    <t>0,54</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -184,109 +172,103 @@
     <t>661,87</t>
   </si>
   <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>0,16</t>
+  </si>
+  <si>
+    <t>0,48</t>
+  </si>
+  <si>
+    <t>4,11</t>
+  </si>
+  <si>
+    <t>16,24</t>
+  </si>
+  <si>
+    <t>81,13</t>
+  </si>
+  <si>
+    <t>57,91</t>
+  </si>
+  <si>
+    <t>2,44</t>
+  </si>
+  <si>
+    <t>76,12</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>428,59</t>
+  </si>
+  <si>
+    <t>84,42</t>
+  </si>
+  <si>
+    <t>265,63</t>
+  </si>
+  <si>
+    <t>88,31</t>
+  </si>
+  <si>
+    <t>586,25</t>
+  </si>
+  <si>
+    <t>167,49</t>
+  </si>
+  <si>
+    <t>83,74</t>
+  </si>
+  <si>
+    <t>251,25</t>
+  </si>
+  <si>
+    <t>1.877,01</t>
+  </si>
+  <si>
+    <t>5.631,08</t>
+  </si>
+  <si>
+    <t>49,82</t>
+  </si>
+  <si>
+    <t>25,46</t>
+  </si>
+  <si>
+    <t>1.155,21</t>
+  </si>
+  <si>
+    <t>1.877,21</t>
+  </si>
+  <si>
+    <t>5.631,63</t>
+  </si>
+  <si>
+    <t>300,35</t>
+  </si>
+  <si>
+    <t>621,04</t>
+  </si>
+  <si>
+    <t>600,70</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>454,86</t>
   </si>
   <si>
     <t>64,98</t>
-  </si>
-  <si>
-    <t>194,93</t>
-  </si>
-  <si>
-    <t>551,72</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>0,16</t>
-  </si>
-  <si>
-    <t>0,48</t>
-  </si>
-  <si>
-    <t>4,11</t>
-  </si>
-  <si>
-    <t>16,24</t>
-  </si>
-  <si>
-    <t>81,13</t>
-  </si>
-  <si>
-    <t>57,91</t>
-  </si>
-  <si>
-    <t>2,44</t>
-  </si>
-  <si>
-    <t>76,12</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>428,59</t>
-  </si>
-  <si>
-    <t>84,42</t>
-  </si>
-  <si>
-    <t>265,63</t>
-  </si>
-  <si>
-    <t>88,31</t>
-  </si>
-  <si>
-    <t>586,25</t>
-  </si>
-  <si>
-    <t>167,49</t>
-  </si>
-  <si>
-    <t>83,74</t>
-  </si>
-  <si>
-    <t>251,25</t>
-  </si>
-  <si>
-    <t>1.877,01</t>
-  </si>
-  <si>
-    <t>5.631,08</t>
-  </si>
-  <si>
-    <t>49,82</t>
-  </si>
-  <si>
-    <t>25,46</t>
-  </si>
-  <si>
-    <t>1.155,21</t>
-  </si>
-  <si>
-    <t>1.877,21</t>
-  </si>
-  <si>
-    <t>5.631,63</t>
-  </si>
-  <si>
-    <t>300,35</t>
-  </si>
-  <si>
-    <t>621,04</t>
-  </si>
-  <si>
-    <t>600,70</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>11</t>
   </si>
   <si>
     <t>194,94</t>
@@ -724,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE11"/>
+  <dimension ref="A1:AE8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="31" width="18" customWidth="1"/>
@@ -869,910 +851,625 @@
         <v>43</v>
       </c>
       <c r="O2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="U2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="X2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Z2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AA2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AB2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AC2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AD2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AE2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" s="2" t="s">
+      <c r="D3" t="s">
         <v>49</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="E3" t="s">
         <v>50</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>43</v>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" t="s">
+        <v>56</v>
+      </c>
+      <c r="N3" t="s">
+        <v>57</v>
+      </c>
+      <c r="O3" t="s">
+        <v>58</v>
+      </c>
+      <c r="P3" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>60</v>
+      </c>
+      <c r="R3" t="s">
+        <v>61</v>
+      </c>
+      <c r="S3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U3" t="s">
+        <v>46</v>
+      </c>
+      <c r="V3" t="s">
+        <v>46</v>
+      </c>
+      <c r="W3" t="s">
+        <v>46</v>
+      </c>
+      <c r="X3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="G4" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="I4" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="J4" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="K4" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="L4" t="s">
         <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="N4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="O4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S4" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="T4" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="U4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="X4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Z4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AA4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AB4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AC4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AD4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AE4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AD5" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="F6" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="H6" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J6" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K6" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="L6" t="s">
         <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="N6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="O6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S6" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="T6" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="U6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="X6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Z6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AA6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AB6" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="AC6" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="AD6" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="AE6" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AD7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
         <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="I8" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="J8" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="K8" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="L8" t="s">
         <v>41</v>
       </c>
       <c r="M8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="O8" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="Q8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="U8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="X8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Y8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Z8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AA8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AB8" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="AC8" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AD8" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="AE8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE9" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" t="s">
-        <v>58</v>
-      </c>
-      <c r="J10" t="s">
-        <v>58</v>
-      </c>
-      <c r="K10" t="s">
-        <v>92</v>
-      </c>
-      <c r="L10" t="s">
-        <v>41</v>
-      </c>
-      <c r="M10" t="s">
-        <v>60</v>
-      </c>
-      <c r="N10" t="s">
-        <v>43</v>
-      </c>
-      <c r="O10" t="s">
-        <v>43</v>
-      </c>
-      <c r="P10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>43</v>
-      </c>
-      <c r="R10" t="s">
-        <v>43</v>
-      </c>
-      <c r="S10" t="s">
-        <v>43</v>
-      </c>
-      <c r="T10" t="s">
-        <v>43</v>
-      </c>
-      <c r="U10" t="s">
-        <v>43</v>
-      </c>
-      <c r="V10" t="s">
-        <v>43</v>
-      </c>
-      <c r="W10" t="s">
-        <v>43</v>
-      </c>
-      <c r="X10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE11" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
